--- a/tables/output/TableS9.xlsx
+++ b/tables/output/TableS9.xlsx
@@ -1408,20 +1408,14 @@
       <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C3" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B3"/>
+      <c r="C3"/>
       <c r="D3" t="s">
         <v>8</v>
       </c>
@@ -1436,9 +1430,7 @@
       <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -1450,20 +1442,14 @@
       <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C6" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B6"/>
+      <c r="C6"/>
       <c r="D6" t="s">
         <v>16</v>
       </c>
@@ -1478,9 +1464,7 @@
       <c r="C7" t="s">
         <v>19</v>
       </c>
-      <c r="D7" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -1492,9 +1476,7 @@
       <c r="C8" t="s">
         <v>21</v>
       </c>
-      <c r="D8" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -1506,9 +1488,7 @@
       <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="D9" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -1520,9 +1500,7 @@
       <c r="C10" t="s">
         <v>26</v>
       </c>
-      <c r="D10" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
@@ -1534,9 +1512,7 @@
       <c r="C11" t="s">
         <v>29</v>
       </c>
-      <c r="D11" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -1548,20 +1524,14 @@
       <c r="C12" t="s">
         <v>32</v>
       </c>
-      <c r="D12" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
         <v>33</v>
       </c>
-      <c r="B13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C13" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B13"/>
+      <c r="C13"/>
       <c r="D13" t="s">
         <v>34</v>
       </c>
@@ -1576,9 +1546,7 @@
       <c r="C14" t="s">
         <v>37</v>
       </c>
-      <c r="D14" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
@@ -1590,9 +1558,7 @@
       <c r="C15" t="s">
         <v>40</v>
       </c>
-      <c r="D15" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -1604,20 +1570,14 @@
       <c r="C16" t="s">
         <v>26</v>
       </c>
-      <c r="D16" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
         <v>43</v>
       </c>
-      <c r="B17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C17" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B17"/>
+      <c r="C17"/>
       <c r="D17" t="s">
         <v>44</v>
       </c>
@@ -1632,9 +1592,7 @@
       <c r="C18" t="s">
         <v>47</v>
       </c>
-      <c r="D18" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -1646,9 +1604,7 @@
       <c r="C19" t="s">
         <v>24</v>
       </c>
-      <c r="D19" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -1660,9 +1616,7 @@
       <c r="C20" t="s">
         <v>21</v>
       </c>
-      <c r="D20" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
@@ -1674,9 +1628,7 @@
       <c r="C21" t="s">
         <v>53</v>
       </c>
-      <c r="D21" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
@@ -1688,9 +1640,7 @@
       <c r="C22" t="s">
         <v>56</v>
       </c>
-      <c r="D22" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
@@ -1755,20 +1705,14 @@
       <c r="C2" t="s">
         <v>259</v>
       </c>
-      <c r="D2" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C3" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B3"/>
+      <c r="C3"/>
       <c r="D3" t="s">
         <v>231</v>
       </c>
@@ -1783,9 +1727,7 @@
       <c r="C4" t="s">
         <v>261</v>
       </c>
-      <c r="D4" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -1797,20 +1739,14 @@
       <c r="C5" t="s">
         <v>263</v>
       </c>
-      <c r="D5" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C6" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B6"/>
+      <c r="C6"/>
       <c r="D6" t="s">
         <v>264</v>
       </c>
@@ -1825,9 +1761,7 @@
       <c r="C7" t="s">
         <v>266</v>
       </c>
-      <c r="D7" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -1839,20 +1773,14 @@
       <c r="C8" t="s">
         <v>268</v>
       </c>
-      <c r="D8" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>33</v>
       </c>
-      <c r="B9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C9" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B9"/>
+      <c r="C9"/>
       <c r="D9" t="s">
         <v>105</v>
       </c>
@@ -1867,9 +1795,7 @@
       <c r="C10" t="s">
         <v>269</v>
       </c>
-      <c r="D10" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
@@ -1881,9 +1807,7 @@
       <c r="C11" t="s">
         <v>268</v>
       </c>
-      <c r="D11" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -1895,20 +1819,14 @@
       <c r="C12" t="s">
         <v>271</v>
       </c>
-      <c r="D12" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
         <v>43</v>
       </c>
-      <c r="B13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C13" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B13"/>
+      <c r="C13"/>
       <c r="D13" t="s">
         <v>272</v>
       </c>
@@ -1923,9 +1841,7 @@
       <c r="C14" t="s">
         <v>269</v>
       </c>
-      <c r="D14" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
@@ -1937,9 +1853,7 @@
       <c r="C15" t="s">
         <v>149</v>
       </c>
-      <c r="D15" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -1951,9 +1865,7 @@
       <c r="C16" t="s">
         <v>273</v>
       </c>
-      <c r="D16" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -1965,9 +1877,7 @@
       <c r="C17" t="s">
         <v>149</v>
       </c>
-      <c r="D17" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -2032,20 +1942,14 @@
       <c r="C2" t="s">
         <v>279</v>
       </c>
-      <c r="D2" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C3" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B3"/>
+      <c r="C3"/>
       <c r="D3" t="s">
         <v>137</v>
       </c>
@@ -2060,9 +1964,7 @@
       <c r="C4" t="s">
         <v>185</v>
       </c>
-      <c r="D4" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -2074,20 +1976,14 @@
       <c r="C5" t="s">
         <v>185</v>
       </c>
-      <c r="D5" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C6" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B6"/>
+      <c r="C6"/>
       <c r="D6" t="s">
         <v>105</v>
       </c>
@@ -2102,9 +1998,7 @@
       <c r="C7" t="s">
         <v>149</v>
       </c>
-      <c r="D7" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -2116,9 +2010,7 @@
       <c r="C8" t="s">
         <v>173</v>
       </c>
-      <c r="D8" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -2130,20 +2022,14 @@
       <c r="C9" t="s">
         <v>175</v>
       </c>
-      <c r="D9" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
         <v>33</v>
       </c>
-      <c r="B10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C10" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B10"/>
+      <c r="C10"/>
       <c r="D10" t="s">
         <v>281</v>
       </c>
@@ -2158,9 +2044,7 @@
       <c r="C11" t="s">
         <v>173</v>
       </c>
-      <c r="D11" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -2172,9 +2056,7 @@
       <c r="C12" t="s">
         <v>175</v>
       </c>
-      <c r="D12" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
@@ -2186,20 +2068,14 @@
       <c r="C13" t="s">
         <v>149</v>
       </c>
-      <c r="D13" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
         <v>43</v>
       </c>
-      <c r="B14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C14" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B14"/>
+      <c r="C14"/>
       <c r="D14" t="s">
         <v>281</v>
       </c>
@@ -2214,9 +2090,7 @@
       <c r="C15" t="s">
         <v>149</v>
       </c>
-      <c r="D15" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -2228,9 +2102,7 @@
       <c r="C16" t="s">
         <v>173</v>
       </c>
-      <c r="D16" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -2242,9 +2114,7 @@
       <c r="C17" t="s">
         <v>175</v>
       </c>
-      <c r="D17" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -2309,20 +2179,14 @@
       <c r="C2" t="s">
         <v>286</v>
       </c>
-      <c r="D2" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C3" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B3"/>
+      <c r="C3"/>
       <c r="D3" t="s">
         <v>201</v>
       </c>
@@ -2337,9 +2201,7 @@
       <c r="C4" t="s">
         <v>287</v>
       </c>
-      <c r="D4" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -2351,20 +2213,14 @@
       <c r="C5" t="s">
         <v>287</v>
       </c>
-      <c r="D5" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C6" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B6"/>
+      <c r="C6"/>
       <c r="D6" t="s">
         <v>98</v>
       </c>
@@ -2379,9 +2235,7 @@
       <c r="C7" t="s">
         <v>288</v>
       </c>
-      <c r="D7" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -2393,9 +2247,7 @@
       <c r="C8" t="s">
         <v>289</v>
       </c>
-      <c r="D8" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -2407,20 +2259,14 @@
       <c r="C9" t="s">
         <v>291</v>
       </c>
-      <c r="D9" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
         <v>33</v>
       </c>
-      <c r="B10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C10" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B10"/>
+      <c r="C10"/>
       <c r="D10" t="s">
         <v>137</v>
       </c>
@@ -2435,9 +2281,7 @@
       <c r="C11" t="s">
         <v>292</v>
       </c>
-      <c r="D11" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -2449,9 +2293,7 @@
       <c r="C12" t="s">
         <v>293</v>
       </c>
-      <c r="D12" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
@@ -2463,20 +2305,14 @@
       <c r="C13" t="s">
         <v>288</v>
       </c>
-      <c r="D13" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
         <v>43</v>
       </c>
-      <c r="B14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C14" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B14"/>
+      <c r="C14"/>
       <c r="D14" t="s">
         <v>232</v>
       </c>
@@ -2491,9 +2327,7 @@
       <c r="C15" t="s">
         <v>294</v>
       </c>
-      <c r="D15" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -2505,9 +2339,7 @@
       <c r="C16" t="s">
         <v>289</v>
       </c>
-      <c r="D16" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -2519,9 +2351,7 @@
       <c r="C17" t="s">
         <v>295</v>
       </c>
-      <c r="D17" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -2586,20 +2416,14 @@
       <c r="C2" t="s">
         <v>301</v>
       </c>
-      <c r="D2" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C3" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B3"/>
+      <c r="C3"/>
       <c r="D3" t="s">
         <v>272</v>
       </c>
@@ -2614,9 +2438,7 @@
       <c r="C4" t="s">
         <v>302</v>
       </c>
-      <c r="D4" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -2628,20 +2450,14 @@
       <c r="C5" t="s">
         <v>303</v>
       </c>
-      <c r="D5" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C6" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B6"/>
+      <c r="C6"/>
       <c r="D6" t="s">
         <v>105</v>
       </c>
@@ -2656,9 +2472,7 @@
       <c r="C7" t="s">
         <v>302</v>
       </c>
-      <c r="D7" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -2670,9 +2484,7 @@
       <c r="C8" t="s">
         <v>304</v>
       </c>
-      <c r="D8" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -2684,20 +2496,14 @@
       <c r="C9" t="s">
         <v>306</v>
       </c>
-      <c r="D9" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
         <v>33</v>
       </c>
-      <c r="B10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C10" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B10"/>
+      <c r="C10"/>
       <c r="D10" t="s">
         <v>276</v>
       </c>
@@ -2712,9 +2518,7 @@
       <c r="C11" t="s">
         <v>302</v>
       </c>
-      <c r="D11" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -2726,20 +2530,14 @@
       <c r="C12" t="s">
         <v>303</v>
       </c>
-      <c r="D12" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
         <v>43</v>
       </c>
-      <c r="B13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C13" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B13"/>
+      <c r="C13"/>
       <c r="D13" t="s">
         <v>105</v>
       </c>
@@ -2754,9 +2552,7 @@
       <c r="C14" t="s">
         <v>302</v>
       </c>
-      <c r="D14" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
@@ -2768,9 +2564,7 @@
       <c r="C15" t="s">
         <v>307</v>
       </c>
-      <c r="D15" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -2782,9 +2576,7 @@
       <c r="C16" t="s">
         <v>308</v>
       </c>
-      <c r="D16" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -2849,20 +2641,14 @@
       <c r="C2" t="s">
         <v>301</v>
       </c>
-      <c r="D2" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C3" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B3"/>
+      <c r="C3"/>
       <c r="D3" t="s">
         <v>105</v>
       </c>
@@ -2877,9 +2663,7 @@
       <c r="C4" t="s">
         <v>306</v>
       </c>
-      <c r="D4" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -2891,20 +2675,14 @@
       <c r="C5" t="s">
         <v>313</v>
       </c>
-      <c r="D5" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C6" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B6"/>
+      <c r="C6"/>
       <c r="D6" t="s">
         <v>314</v>
       </c>
@@ -2919,9 +2697,7 @@
       <c r="C7" t="s">
         <v>307</v>
       </c>
-      <c r="D7" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -2933,9 +2709,7 @@
       <c r="C8" t="s">
         <v>302</v>
       </c>
-      <c r="D8" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -2947,20 +2721,14 @@
       <c r="C9" t="s">
         <v>308</v>
       </c>
-      <c r="D9" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
         <v>33</v>
       </c>
-      <c r="B10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C10" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B10"/>
+      <c r="C10"/>
       <c r="D10" t="s">
         <v>315</v>
       </c>
@@ -2975,9 +2743,7 @@
       <c r="C11" t="s">
         <v>302</v>
       </c>
-      <c r="D11" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -2989,9 +2755,7 @@
       <c r="C12" t="s">
         <v>316</v>
       </c>
-      <c r="D12" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
@@ -3003,20 +2767,14 @@
       <c r="C13" t="s">
         <v>302</v>
       </c>
-      <c r="D13" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
         <v>43</v>
       </c>
-      <c r="B14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C14" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B14"/>
+      <c r="C14"/>
       <c r="D14" t="s">
         <v>135</v>
       </c>
@@ -3031,9 +2789,7 @@
       <c r="C15" t="s">
         <v>307</v>
       </c>
-      <c r="D15" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -3045,9 +2801,7 @@
       <c r="C16" t="s">
         <v>307</v>
       </c>
-      <c r="D16" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -3059,9 +2813,7 @@
       <c r="C17" t="s">
         <v>306</v>
       </c>
-      <c r="D17" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -3126,20 +2878,14 @@
       <c r="C2" t="s">
         <v>322</v>
       </c>
-      <c r="D2" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C3" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B3"/>
+      <c r="C3"/>
       <c r="D3" t="s">
         <v>276</v>
       </c>
@@ -3154,9 +2900,7 @@
       <c r="C4" t="s">
         <v>323</v>
       </c>
-      <c r="D4" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -3168,20 +2912,14 @@
       <c r="C5" t="s">
         <v>323</v>
       </c>
-      <c r="D5" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C6" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B6"/>
+      <c r="C6"/>
       <c r="D6" t="s">
         <v>298</v>
       </c>
@@ -3196,9 +2934,7 @@
       <c r="C7" t="s">
         <v>324</v>
       </c>
-      <c r="D7" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -3210,20 +2946,14 @@
       <c r="C8" t="s">
         <v>325</v>
       </c>
-      <c r="D8" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>33</v>
       </c>
-      <c r="B9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C9" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B9"/>
+      <c r="C9"/>
       <c r="D9" t="s">
         <v>105</v>
       </c>
@@ -3238,9 +2968,7 @@
       <c r="C10" t="s">
         <v>324</v>
       </c>
-      <c r="D10" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
@@ -3252,9 +2980,7 @@
       <c r="C11" t="s">
         <v>326</v>
       </c>
-      <c r="D11" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -3266,20 +2992,14 @@
       <c r="C12" t="s">
         <v>269</v>
       </c>
-      <c r="D12" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
         <v>43</v>
       </c>
-      <c r="B13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C13" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B13"/>
+      <c r="C13"/>
       <c r="D13" t="s">
         <v>105</v>
       </c>
@@ -3294,9 +3014,7 @@
       <c r="C14" t="s">
         <v>324</v>
       </c>
-      <c r="D14" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
@@ -3308,9 +3026,7 @@
       <c r="C15" t="s">
         <v>325</v>
       </c>
-      <c r="D15" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -3375,20 +3091,14 @@
       <c r="C2" t="s">
         <v>330</v>
       </c>
-      <c r="D2" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C3" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B3"/>
+      <c r="C3"/>
       <c r="D3" t="s">
         <v>154</v>
       </c>
@@ -3403,9 +3113,7 @@
       <c r="C4" t="s">
         <v>332</v>
       </c>
-      <c r="D4" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -3417,20 +3125,14 @@
       <c r="C5" t="s">
         <v>333</v>
       </c>
-      <c r="D5" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C6" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B6"/>
+      <c r="C6"/>
       <c r="D6" t="s">
         <v>105</v>
       </c>
@@ -3445,9 +3147,7 @@
       <c r="C7" t="s">
         <v>202</v>
       </c>
-      <c r="D7" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -3459,9 +3159,7 @@
       <c r="C8" t="s">
         <v>199</v>
       </c>
-      <c r="D8" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -3473,9 +3171,7 @@
       <c r="C9" t="s">
         <v>202</v>
       </c>
-      <c r="D9" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -3487,20 +3183,14 @@
       <c r="C10" t="s">
         <v>334</v>
       </c>
-      <c r="D10" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C11" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B11"/>
+      <c r="C11"/>
       <c r="D11" t="s">
         <v>227</v>
       </c>
@@ -3515,9 +3205,7 @@
       <c r="C12" t="s">
         <v>202</v>
       </c>
-      <c r="D12" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
@@ -3529,20 +3217,14 @@
       <c r="C13" t="s">
         <v>204</v>
       </c>
-      <c r="D13" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
         <v>43</v>
       </c>
-      <c r="B14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C14" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B14"/>
+      <c r="C14"/>
       <c r="D14" t="s">
         <v>337</v>
       </c>
@@ -3557,9 +3239,7 @@
       <c r="C15" t="s">
         <v>199</v>
       </c>
-      <c r="D15" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -3571,9 +3251,7 @@
       <c r="C16" t="s">
         <v>338</v>
       </c>
-      <c r="D16" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -3585,9 +3263,7 @@
       <c r="C17" t="s">
         <v>199</v>
       </c>
-      <c r="D17" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -3599,9 +3275,7 @@
       <c r="C18" t="s">
         <v>339</v>
       </c>
-      <c r="D18" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -3613,9 +3287,7 @@
       <c r="C19" t="s">
         <v>199</v>
       </c>
-      <c r="D19" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -3680,20 +3352,14 @@
       <c r="C2" t="s">
         <v>66</v>
       </c>
-      <c r="D2" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C3" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B3"/>
+      <c r="C3"/>
       <c r="D3" t="s">
         <v>67</v>
       </c>
@@ -3708,9 +3374,7 @@
       <c r="C4" t="s">
         <v>69</v>
       </c>
-      <c r="D4" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -3722,20 +3386,14 @@
       <c r="C5" t="s">
         <v>71</v>
       </c>
-      <c r="D5" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C6" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B6"/>
+      <c r="C6"/>
       <c r="D6" t="s">
         <v>72</v>
       </c>
@@ -3750,9 +3408,7 @@
       <c r="C7" t="s">
         <v>73</v>
       </c>
-      <c r="D7" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -3764,9 +3420,7 @@
       <c r="C8" t="s">
         <v>75</v>
       </c>
-      <c r="D8" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -3778,9 +3432,7 @@
       <c r="C9" t="s">
         <v>76</v>
       </c>
-      <c r="D9" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -3792,9 +3444,7 @@
       <c r="C10" t="s">
         <v>75</v>
       </c>
-      <c r="D10" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
@@ -3806,9 +3456,7 @@
       <c r="C11" t="s">
         <v>78</v>
       </c>
-      <c r="D11" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -3820,20 +3468,14 @@
       <c r="C12" t="s">
         <v>80</v>
       </c>
-      <c r="D12" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
         <v>33</v>
       </c>
-      <c r="B13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C13" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B13"/>
+      <c r="C13"/>
       <c r="D13" t="s">
         <v>81</v>
       </c>
@@ -3848,9 +3490,7 @@
       <c r="C14" t="s">
         <v>82</v>
       </c>
-      <c r="D14" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
@@ -3862,9 +3502,7 @@
       <c r="C15" t="s">
         <v>84</v>
       </c>
-      <c r="D15" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -3876,20 +3514,14 @@
       <c r="C16" t="s">
         <v>85</v>
       </c>
-      <c r="D16" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
         <v>43</v>
       </c>
-      <c r="B17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C17" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B17"/>
+      <c r="C17"/>
       <c r="D17" t="s">
         <v>86</v>
       </c>
@@ -3904,9 +3536,7 @@
       <c r="C18" t="s">
         <v>76</v>
       </c>
-      <c r="D18" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -3918,9 +3548,7 @@
       <c r="C19" t="s">
         <v>87</v>
       </c>
-      <c r="D19" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -3932,9 +3560,7 @@
       <c r="C20" t="s">
         <v>88</v>
       </c>
-      <c r="D20" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
@@ -3946,9 +3572,7 @@
       <c r="C21" t="s">
         <v>89</v>
       </c>
-      <c r="D21" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
@@ -3960,9 +3584,7 @@
       <c r="C22" t="s">
         <v>75</v>
       </c>
-      <c r="D22" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
@@ -4027,20 +3649,14 @@
       <c r="C2" t="s">
         <v>97</v>
       </c>
-      <c r="D2" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C3" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B3"/>
+      <c r="C3"/>
       <c r="D3" t="s">
         <v>98</v>
       </c>
@@ -4055,9 +3671,7 @@
       <c r="C4" t="s">
         <v>100</v>
       </c>
-      <c r="D4" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -4069,20 +3683,14 @@
       <c r="C5" t="s">
         <v>100</v>
       </c>
-      <c r="D5" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C6" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B6"/>
+      <c r="C6"/>
       <c r="D6" t="s">
         <v>102</v>
       </c>
@@ -4097,9 +3705,7 @@
       <c r="C7" t="s">
         <v>75</v>
       </c>
-      <c r="D7" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -4111,9 +3717,7 @@
       <c r="C8" t="s">
         <v>85</v>
       </c>
-      <c r="D8" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -4125,9 +3729,7 @@
       <c r="C9" t="s">
         <v>76</v>
       </c>
-      <c r="D9" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -4139,9 +3741,7 @@
       <c r="C10" t="s">
         <v>73</v>
       </c>
-      <c r="D10" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
@@ -4153,9 +3753,7 @@
       <c r="C11" t="s">
         <v>76</v>
       </c>
-      <c r="D11" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -4167,20 +3765,14 @@
       <c r="C12" t="s">
         <v>104</v>
       </c>
-      <c r="D12" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
         <v>33</v>
       </c>
-      <c r="B13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C13" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B13"/>
+      <c r="C13"/>
       <c r="D13" t="s">
         <v>105</v>
       </c>
@@ -4195,9 +3787,7 @@
       <c r="C14" t="s">
         <v>75</v>
       </c>
-      <c r="D14" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
@@ -4209,9 +3799,7 @@
       <c r="C15" t="s">
         <v>107</v>
       </c>
-      <c r="D15" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -4223,20 +3811,14 @@
       <c r="C16" t="s">
         <v>85</v>
       </c>
-      <c r="D16" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
         <v>43</v>
       </c>
-      <c r="B17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C17" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B17"/>
+      <c r="C17"/>
       <c r="D17" t="s">
         <v>108</v>
       </c>
@@ -4251,9 +3833,7 @@
       <c r="C18" t="s">
         <v>82</v>
       </c>
-      <c r="D18" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -4265,9 +3845,7 @@
       <c r="C19" t="s">
         <v>75</v>
       </c>
-      <c r="D19" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -4279,9 +3857,7 @@
       <c r="C20" t="s">
         <v>75</v>
       </c>
-      <c r="D20" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
@@ -4293,9 +3869,7 @@
       <c r="C21" t="s">
         <v>111</v>
       </c>
-      <c r="D21" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
@@ -4307,9 +3881,7 @@
       <c r="C22" t="s">
         <v>85</v>
       </c>
-      <c r="D22" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
@@ -4374,20 +3946,14 @@
       <c r="C2" t="s">
         <v>117</v>
       </c>
-      <c r="D2" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C3" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B3"/>
+      <c r="C3"/>
       <c r="D3" t="s">
         <v>118</v>
       </c>
@@ -4402,9 +3968,7 @@
       <c r="C4" t="s">
         <v>120</v>
       </c>
-      <c r="D4" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -4416,20 +3980,14 @@
       <c r="C5" t="s">
         <v>122</v>
       </c>
-      <c r="D5" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C6" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B6"/>
+      <c r="C6"/>
       <c r="D6" t="s">
         <v>105</v>
       </c>
@@ -4444,9 +4002,7 @@
       <c r="C7" t="s">
         <v>123</v>
       </c>
-      <c r="D7" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -4458,9 +4014,7 @@
       <c r="C8" t="s">
         <v>123</v>
       </c>
-      <c r="D8" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -4472,9 +4026,7 @@
       <c r="C9" t="s">
         <v>124</v>
       </c>
-      <c r="D9" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -4486,20 +4038,14 @@
       <c r="C10" t="s">
         <v>125</v>
       </c>
-      <c r="D10" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C11" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B11"/>
+      <c r="C11"/>
       <c r="D11" t="s">
         <v>34</v>
       </c>
@@ -4514,9 +4060,7 @@
       <c r="C12" t="s">
         <v>126</v>
       </c>
-      <c r="D12" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
@@ -4528,9 +4072,7 @@
       <c r="C13" t="s">
         <v>127</v>
       </c>
-      <c r="D13" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
@@ -4542,20 +4084,14 @@
       <c r="C14" t="s">
         <v>128</v>
       </c>
-      <c r="D14" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
         <v>43</v>
       </c>
-      <c r="B15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C15" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B15"/>
+      <c r="C15"/>
       <c r="D15" t="s">
         <v>129</v>
       </c>
@@ -4570,9 +4106,7 @@
       <c r="C16" t="s">
         <v>123</v>
       </c>
-      <c r="D16" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -4584,9 +4118,7 @@
       <c r="C17" t="s">
         <v>130</v>
       </c>
-      <c r="D17" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -4598,9 +4130,7 @@
       <c r="C18" t="s">
         <v>131</v>
       </c>
-      <c r="D18" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -4612,9 +4142,7 @@
       <c r="C19" t="s">
         <v>132</v>
       </c>
-      <c r="D19" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -4679,20 +4207,14 @@
       <c r="C2" t="s">
         <v>139</v>
       </c>
-      <c r="D2" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C3" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B3"/>
+      <c r="C3"/>
       <c r="D3" t="s">
         <v>72</v>
       </c>
@@ -4707,9 +4229,7 @@
       <c r="C4" t="s">
         <v>141</v>
       </c>
-      <c r="D4" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -4721,9 +4241,7 @@
       <c r="C5" t="s">
         <v>142</v>
       </c>
-      <c r="D5" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -4735,20 +4253,14 @@
       <c r="C6" t="s">
         <v>145</v>
       </c>
-      <c r="D6" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C7" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B7"/>
+      <c r="C7"/>
       <c r="D7" t="s">
         <v>146</v>
       </c>
@@ -4763,9 +4275,7 @@
       <c r="C8" t="s">
         <v>148</v>
       </c>
-      <c r="D8" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -4777,9 +4287,7 @@
       <c r="C9" t="s">
         <v>148</v>
       </c>
-      <c r="D9" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -4791,9 +4299,7 @@
       <c r="C10" t="s">
         <v>149</v>
       </c>
-      <c r="D10" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
@@ -4805,9 +4311,7 @@
       <c r="C11" t="s">
         <v>151</v>
       </c>
-      <c r="D11" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -4819,20 +4323,14 @@
       <c r="C12" t="s">
         <v>153</v>
       </c>
-      <c r="D12" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
         <v>33</v>
       </c>
-      <c r="B13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C13" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B13"/>
+      <c r="C13"/>
       <c r="D13" t="s">
         <v>154</v>
       </c>
@@ -4847,9 +4345,7 @@
       <c r="C14" t="s">
         <v>156</v>
       </c>
-      <c r="D14" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
@@ -4861,9 +4357,7 @@
       <c r="C15" t="s">
         <v>158</v>
       </c>
-      <c r="D15" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -4875,20 +4369,14 @@
       <c r="C16" t="s">
         <v>156</v>
       </c>
-      <c r="D16" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
         <v>43</v>
       </c>
-      <c r="B17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C17" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B17"/>
+      <c r="C17"/>
       <c r="D17" t="s">
         <v>160</v>
       </c>
@@ -4903,9 +4391,7 @@
       <c r="C18" t="s">
         <v>148</v>
       </c>
-      <c r="D18" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -4917,9 +4403,7 @@
       <c r="C19" t="s">
         <v>148</v>
       </c>
-      <c r="D19" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -4931,9 +4415,7 @@
       <c r="C20" t="s">
         <v>149</v>
       </c>
-      <c r="D20" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
@@ -4945,9 +4427,7 @@
       <c r="C21" t="s">
         <v>163</v>
       </c>
-      <c r="D21" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
@@ -4959,9 +4439,7 @@
       <c r="C22" t="s">
         <v>145</v>
       </c>
-      <c r="D22" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
@@ -5026,20 +4504,14 @@
       <c r="C2" t="s">
         <v>171</v>
       </c>
-      <c r="D2" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C3" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B3"/>
+      <c r="C3"/>
       <c r="D3" t="s">
         <v>172</v>
       </c>
@@ -5054,9 +4526,7 @@
       <c r="C4" t="s">
         <v>174</v>
       </c>
-      <c r="D4" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -5068,20 +4538,14 @@
       <c r="C5" t="s">
         <v>176</v>
       </c>
-      <c r="D5" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C6" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B6"/>
+      <c r="C6"/>
       <c r="D6" t="s">
         <v>44</v>
       </c>
@@ -5096,9 +4560,7 @@
       <c r="C7" t="s">
         <v>177</v>
       </c>
-      <c r="D7" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -5110,9 +4572,7 @@
       <c r="C8" t="s">
         <v>178</v>
       </c>
-      <c r="D8" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -5124,9 +4584,7 @@
       <c r="C9" t="s">
         <v>179</v>
       </c>
-      <c r="D9" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -5138,20 +4596,14 @@
       <c r="C10" t="s">
         <v>180</v>
       </c>
-      <c r="D10" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C11" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B11"/>
+      <c r="C11"/>
       <c r="D11" t="s">
         <v>181</v>
       </c>
@@ -5166,9 +4618,7 @@
       <c r="C12" t="s">
         <v>182</v>
       </c>
-      <c r="D12" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
@@ -5180,20 +4630,14 @@
       <c r="C13" t="s">
         <v>183</v>
       </c>
-      <c r="D13" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
         <v>43</v>
       </c>
-      <c r="B14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C14" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B14"/>
+      <c r="C14"/>
       <c r="D14" t="s">
         <v>184</v>
       </c>
@@ -5208,9 +4652,7 @@
       <c r="C15" t="s">
         <v>179</v>
       </c>
-      <c r="D15" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -5222,9 +4664,7 @@
       <c r="C16" t="s">
         <v>179</v>
       </c>
-      <c r="D16" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -5236,9 +4676,7 @@
       <c r="C17" t="s">
         <v>186</v>
       </c>
-      <c r="D17" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -5250,9 +4688,7 @@
       <c r="C18" t="s">
         <v>177</v>
       </c>
-      <c r="D18" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -5317,20 +4753,14 @@
       <c r="C2" t="s">
         <v>192</v>
       </c>
-      <c r="D2" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C3" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B3"/>
+      <c r="C3"/>
       <c r="D3" t="s">
         <v>193</v>
       </c>
@@ -5345,9 +4775,7 @@
       <c r="C4" t="s">
         <v>195</v>
       </c>
-      <c r="D4" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -5359,20 +4787,14 @@
       <c r="C5" t="s">
         <v>196</v>
       </c>
-      <c r="D5" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C6" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B6"/>
+      <c r="C6"/>
       <c r="D6" t="s">
         <v>105</v>
       </c>
@@ -5387,9 +4809,7 @@
       <c r="C7" t="s">
         <v>198</v>
       </c>
-      <c r="D7" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -5401,9 +4821,7 @@
       <c r="C8" t="s">
         <v>199</v>
       </c>
-      <c r="D8" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -5415,9 +4833,7 @@
       <c r="C9" t="s">
         <v>198</v>
       </c>
-      <c r="D9" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -5429,20 +4845,14 @@
       <c r="C10" t="s">
         <v>198</v>
       </c>
-      <c r="D10" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C11" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B11"/>
+      <c r="C11"/>
       <c r="D11" t="s">
         <v>201</v>
       </c>
@@ -5457,9 +4867,7 @@
       <c r="C12" t="s">
         <v>202</v>
       </c>
-      <c r="D12" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
@@ -5471,9 +4879,7 @@
       <c r="C13" t="s">
         <v>204</v>
       </c>
-      <c r="D13" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
@@ -5485,20 +4891,14 @@
       <c r="C14" t="s">
         <v>149</v>
       </c>
-      <c r="D14" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
         <v>43</v>
       </c>
-      <c r="B15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C15" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B15"/>
+      <c r="C15"/>
       <c r="D15" t="s">
         <v>205</v>
       </c>
@@ -5513,9 +4913,7 @@
       <c r="C16" t="s">
         <v>207</v>
       </c>
-      <c r="D16" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -5527,9 +4925,7 @@
       <c r="C17" t="s">
         <v>208</v>
       </c>
-      <c r="D17" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -5541,9 +4937,7 @@
       <c r="C18" t="s">
         <v>196</v>
       </c>
-      <c r="D18" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -5608,20 +5002,14 @@
       <c r="C2" t="s">
         <v>215</v>
       </c>
-      <c r="D2" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C3" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B3"/>
+      <c r="C3"/>
       <c r="D3" t="s">
         <v>92</v>
       </c>
@@ -5636,9 +5024,7 @@
       <c r="C4" t="s">
         <v>216</v>
       </c>
-      <c r="D4" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -5650,20 +5036,14 @@
       <c r="C5" t="s">
         <v>217</v>
       </c>
-      <c r="D5" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C6" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B6"/>
+      <c r="C6"/>
       <c r="D6" t="s">
         <v>218</v>
       </c>
@@ -5678,9 +5058,7 @@
       <c r="C7" t="s">
         <v>219</v>
       </c>
-      <c r="D7" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -5692,9 +5070,7 @@
       <c r="C8" t="s">
         <v>220</v>
       </c>
-      <c r="D8" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -5706,9 +5082,7 @@
       <c r="C9" t="s">
         <v>221</v>
       </c>
-      <c r="D9" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -5720,20 +5094,14 @@
       <c r="C10" t="s">
         <v>222</v>
       </c>
-      <c r="D10" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C11" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B11"/>
+      <c r="C11"/>
       <c r="D11" t="s">
         <v>223</v>
       </c>
@@ -5748,9 +5116,7 @@
       <c r="C12" t="s">
         <v>224</v>
       </c>
-      <c r="D12" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
@@ -5762,9 +5128,7 @@
       <c r="C13" t="s">
         <v>226</v>
       </c>
-      <c r="D13" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
@@ -5776,20 +5140,14 @@
       <c r="C14" t="s">
         <v>149</v>
       </c>
-      <c r="D14" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
         <v>43</v>
       </c>
-      <c r="B15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C15" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B15"/>
+      <c r="C15"/>
       <c r="D15" t="s">
         <v>227</v>
       </c>
@@ -5804,9 +5162,7 @@
       <c r="C16" t="s">
         <v>219</v>
       </c>
-      <c r="D16" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -5818,9 +5174,7 @@
       <c r="C17" t="s">
         <v>224</v>
       </c>
-      <c r="D17" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -5832,9 +5186,7 @@
       <c r="C18" t="s">
         <v>149</v>
       </c>
-      <c r="D18" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -5846,9 +5198,7 @@
       <c r="C19" t="s">
         <v>228</v>
       </c>
-      <c r="D19" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -5860,9 +5210,7 @@
       <c r="C20" t="s">
         <v>220</v>
       </c>
-      <c r="D20" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
@@ -5927,20 +5275,14 @@
       <c r="C2" t="s">
         <v>234</v>
       </c>
-      <c r="D2" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C3" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B3"/>
+      <c r="C3"/>
       <c r="D3" t="s">
         <v>172</v>
       </c>
@@ -5955,9 +5297,7 @@
       <c r="C4" t="s">
         <v>236</v>
       </c>
-      <c r="D4" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -5969,9 +5309,7 @@
       <c r="C5" t="s">
         <v>237</v>
       </c>
-      <c r="D5" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -5983,20 +5321,14 @@
       <c r="C6" t="s">
         <v>238</v>
       </c>
-      <c r="D6" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C7" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B7"/>
+      <c r="C7"/>
       <c r="D7" t="s">
         <v>105</v>
       </c>
@@ -6011,9 +5343,7 @@
       <c r="C8" t="s">
         <v>239</v>
       </c>
-      <c r="D8" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -6025,9 +5355,7 @@
       <c r="C9" t="s">
         <v>240</v>
       </c>
-      <c r="D9" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -6039,9 +5367,7 @@
       <c r="C10" t="s">
         <v>240</v>
       </c>
-      <c r="D10" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
@@ -6053,9 +5379,7 @@
       <c r="C11" t="s">
         <v>242</v>
       </c>
-      <c r="D11" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -6067,20 +5391,14 @@
       <c r="C12" t="s">
         <v>243</v>
       </c>
-      <c r="D12" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
         <v>33</v>
       </c>
-      <c r="B13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C13" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B13"/>
+      <c r="C13"/>
       <c r="D13" t="s">
         <v>244</v>
       </c>
@@ -6095,9 +5413,7 @@
       <c r="C14" t="s">
         <v>245</v>
       </c>
-      <c r="D14" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
@@ -6109,9 +5425,7 @@
       <c r="C15" t="s">
         <v>246</v>
       </c>
-      <c r="D15" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -6123,20 +5437,14 @@
       <c r="C16" t="s">
         <v>247</v>
       </c>
-      <c r="D16" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
         <v>43</v>
       </c>
-      <c r="B17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C17" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="B17"/>
+      <c r="C17"/>
       <c r="D17" t="s">
         <v>248</v>
       </c>
@@ -6151,9 +5459,7 @@
       <c r="C18" t="s">
         <v>240</v>
       </c>
-      <c r="D18" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -6165,9 +5471,7 @@
       <c r="C19" t="s">
         <v>249</v>
       </c>
-      <c r="D19" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -6179,9 +5483,7 @@
       <c r="C20" t="s">
         <v>250</v>
       </c>
-      <c r="D20" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
@@ -6193,9 +5495,7 @@
       <c r="C21" t="s">
         <v>242</v>
       </c>
-      <c r="D21" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
@@ -6207,9 +5507,7 @@
       <c r="C22" t="s">
         <v>251</v>
       </c>
-      <c r="D22" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
@@ -6221,9 +5519,7 @@
       <c r="C23" t="s">
         <v>252</v>
       </c>
-      <c r="D23" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="D23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
